--- a/JsonConverter/ExcelFiles/Exchange.xlsx
+++ b/JsonConverter/ExcelFiles/Exchange.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="13128" windowHeight="7968"/>
+    <workbookView windowWidth="13776" windowHeight="8400"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="30">
   <si>
     <t>아이디</t>
   </si>
@@ -68,7 +68,7 @@
     <t>ex_gold_to_ingot_01</t>
   </si>
   <si>
-    <t>Buy Ingot small</t>
+    <t>Buy a Ingot</t>
   </si>
   <si>
     <t>골드를 주고 주괴를 하나 구입합니다</t>
@@ -77,7 +77,7 @@
     <t>ex_gold_to_ingot_02</t>
   </si>
   <si>
-    <t>Buy Ingot medium</t>
+    <t>Buy IngotPack</t>
   </si>
   <si>
     <t>골드를 좀 더 내고 주괴 묶음을 구입합니다</t>
@@ -86,22 +86,34 @@
     <t>ex_gold_to_ingot_03</t>
   </si>
   <si>
+    <t>Buy IngotBox</t>
+  </si>
+  <si>
     <t>골드를 많이 주고 주괴 박스를 구입합니다</t>
   </si>
   <si>
     <t>ex_ingot_to_gold_01</t>
   </si>
   <si>
+    <t>Sell a Ingot</t>
+  </si>
+  <si>
     <t>주괴를 판매합니다</t>
   </si>
   <si>
     <t>ex_ingot_to_gold_02</t>
   </si>
   <si>
+    <t>Sell IngotPack</t>
+  </si>
+  <si>
     <t>주괴 묶음을 판매합니다</t>
   </si>
   <si>
     <t>ex_ingot_to_gold_03</t>
+  </si>
+  <si>
+    <t>Sell IngotBox</t>
   </si>
   <si>
     <t>주괴 박스를 판매합니다</t>
@@ -1382,7 +1394,7 @@
         <v>18</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C6">
         <v>200</v>
@@ -1391,12 +1403,15 @@
         <v>10</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="B7" t="s">
+        <v>22</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -1405,12 +1420,15 @@
         <v>10</v>
       </c>
       <c r="E7" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" t="s">
-        <v>22</v>
+        <v>24</v>
+      </c>
+      <c r="B8" t="s">
+        <v>25</v>
       </c>
       <c r="C8">
         <v>5</v>
@@ -1419,12 +1437,15 @@
         <v>55</v>
       </c>
       <c r="E8" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>27</v>
+      </c>
+      <c r="B9" t="s">
+        <v>28</v>
       </c>
       <c r="C9">
         <v>10</v>
@@ -1433,7 +1454,7 @@
         <v>110</v>
       </c>
       <c r="E9" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J9" s="4"/>
     </row>

--- a/JsonConverter/ExcelFiles/Exchange.xlsx
+++ b/JsonConverter/ExcelFiles/Exchange.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="21">
   <si>
     <t>아이디</t>
   </si>
@@ -35,10 +35,10 @@
     <t>이름</t>
   </si>
   <si>
-    <t>교환 수량</t>
-  </si>
-  <si>
-    <t>교환량</t>
+    <t>골드 수량</t>
+  </si>
+  <si>
+    <t>주괴 수량</t>
   </si>
   <si>
     <t>설명</t>
@@ -56,67 +56,40 @@
     <t>Name</t>
   </si>
   <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>Exchanges</t>
+    <t>GoldValue</t>
+  </si>
+  <si>
+    <t>IngotValue</t>
   </si>
   <si>
     <t>Desc</t>
   </si>
   <si>
-    <t>ex_gold_to_ingot_01</t>
-  </si>
-  <si>
-    <t>Buy a Ingot</t>
-  </si>
-  <si>
-    <t>골드를 주고 주괴를 하나 구입합니다</t>
-  </si>
-  <si>
-    <t>ex_gold_to_ingot_02</t>
-  </si>
-  <si>
-    <t>Buy IngotPack</t>
-  </si>
-  <si>
-    <t>골드를 좀 더 내고 주괴 묶음을 구입합니다</t>
-  </si>
-  <si>
-    <t>ex_gold_to_ingot_03</t>
-  </si>
-  <si>
-    <t>Buy IngotBox</t>
-  </si>
-  <si>
-    <t>골드를 많이 주고 주괴 박스를 구입합니다</t>
-  </si>
-  <si>
-    <t>ex_ingot_to_gold_01</t>
-  </si>
-  <si>
-    <t>Sell a Ingot</t>
-  </si>
-  <si>
-    <t>주괴를 판매합니다</t>
-  </si>
-  <si>
-    <t>ex_ingot_to_gold_02</t>
-  </si>
-  <si>
-    <t>Sell IngotPack</t>
-  </si>
-  <si>
-    <t>주괴 묶음을 판매합니다</t>
-  </si>
-  <si>
-    <t>ex_ingot_to_gold_03</t>
-  </si>
-  <si>
-    <t>Sell IngotBox</t>
-  </si>
-  <si>
-    <t>주괴 박스를 판매합니다</t>
+    <t>ex_01</t>
+  </si>
+  <si>
+    <t>Small Exchange</t>
+  </si>
+  <si>
+    <t>소량 교환</t>
+  </si>
+  <si>
+    <t>ex_02</t>
+  </si>
+  <si>
+    <t>Medium Exchange</t>
+  </si>
+  <si>
+    <t>적당량 교환</t>
+  </si>
+  <si>
+    <t>ex_03</t>
+  </si>
+  <si>
+    <t>Large Exchange</t>
+  </si>
+  <si>
+    <t>대량 교환</t>
   </si>
 </sst>
 </file>
@@ -1406,56 +1379,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
-      <c r="A7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7">
-        <v>10</v>
-      </c>
-      <c r="E7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
-      <c r="A8" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8">
-        <v>5</v>
-      </c>
-      <c r="D8">
-        <v>55</v>
-      </c>
-      <c r="E8" t="s">
-        <v>26</v>
-      </c>
-    </row>
     <row r="9" spans="1:12">
-      <c r="A9" t="s">
-        <v>27</v>
-      </c>
-      <c r="B9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9">
-        <v>10</v>
-      </c>
-      <c r="D9">
-        <v>110</v>
-      </c>
-      <c r="E9" t="s">
-        <v>29</v>
-      </c>
       <c r="J9" s="4"/>
     </row>
   </sheetData>
